--- a/summer_camps/001_summer_school_application_form--summer_camps.xlsx
+++ b/summer_camps/001_summer_school_application_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1162,8 +1162,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'camp_a'}</t>
+          <t>camp_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Camp A'}</t>
+          <t>Camp A</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'camp_b'}</t>
+          <t>camp_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Camp B'}</t>
+          <t>Camp B</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'camp_c'}</t>
+          <t>camp_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Camp C'}</t>
+          <t>Camp C</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'camp_x'}</t>
+          <t>camp_x</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Camp X'}</t>
+          <t>Camp X</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'camp_y'}</t>
+          <t>camp_y</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Camp Y'}</t>
+          <t>Camp Y</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'camp_z'}</t>
+          <t>camp_z</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Camp Z'}</t>
+          <t>Camp Z</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'question_a'}</t>
+          <t>question_a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Question A'}</t>
+          <t>Question A</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'question_b'}</t>
+          <t>question_b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Question B'}</t>
+          <t>Question B</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'question_c'}</t>
+          <t>question_c</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Question C'}</t>
+          <t>Question C</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'option_x'}</t>
+          <t>option_x</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Option X'}</t>
+          <t>Option X</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'option_y'}</t>
+          <t>option_y</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Option Y'}</t>
+          <t>Option Y</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'option_z'}</t>
+          <t>option_z</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Option Z'}</t>
+          <t>Option Z</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'question_a'}</t>
+          <t>question_a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Question A'}</t>
+          <t>Question A</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'question_b'}</t>
+          <t>question_b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Question B'}</t>
+          <t>Question B</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'question_c'}</t>
+          <t>question_c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Question C'}</t>
+          <t>Question C</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'option_x'}</t>
+          <t>option_x</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Option X'}</t>
+          <t>Option X</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'option_y'}</t>
+          <t>option_y</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Option Y'}</t>
+          <t>Option Y</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'option_z'}</t>
+          <t>option_z</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Option Z'}</t>
+          <t>Option Z</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'program_c'}</t>
+          <t>program_c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Program C'}</t>
+          <t>Program C</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'program_c'}</t>
+          <t>program_c</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Program C'}</t>
+          <t>Program C</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'program_c'}</t>
+          <t>program_c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Program C'}</t>
+          <t>Program C</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'program_a'}</t>
+          <t>program_a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Program A'}</t>
+          <t>Program A</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'program_b'}</t>
+          <t>program_b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Program B'}</t>
+          <t>Program B</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'program_c'}</t>
+          <t>program_c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Program C'}</t>
+          <t>Program C</t>
         </is>
       </c>
     </row>
